--- a/FACULTY.xlsx
+++ b/FACULTY.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="59">
   <si>
     <t>NAME</t>
   </si>
@@ -188,13 +188,37 @@
   </si>
   <si>
     <t>HOC VEDANTA  HOSPITAL</t>
+  </si>
+  <si>
+    <t>Dr Bhavin Desai</t>
+  </si>
+  <si>
+    <t>Dr Gopal Shah</t>
+  </si>
+  <si>
+    <t>Dr Monil Patel</t>
+  </si>
+  <si>
+    <t>Dr Aakash Patel</t>
+  </si>
+  <si>
+    <t>Dr Tirth Patel</t>
+  </si>
+  <si>
+    <t>Dr Tejas Patel</t>
+  </si>
+  <si>
+    <t>Dr Sandip Modh</t>
+  </si>
+  <si>
+    <t>DR SUBHASH CHAUDHARY</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -229,6 +253,18 @@
       <color indexed="8"/>
       <name val="Calibri"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -266,7 +302,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -297,6 +333,20 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -577,7 +627,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -1115,96 +1165,116 @@
       <c r="H37" s="1"/>
     </row>
     <row r="38" spans="1:8" ht="15.75">
-      <c r="A38" s="12"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="9"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="1"/>
+      <c r="A38" s="7">
+        <v>36</v>
+      </c>
+      <c r="B38" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D38" s="15">
+        <v>9825017212</v>
+      </c>
     </row>
     <row r="39" spans="1:8" ht="15.75">
-      <c r="A39" s="12"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="9"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
+      <c r="A39" s="7">
+        <v>37</v>
+      </c>
+      <c r="B39" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D39" s="15">
+        <v>9825300005</v>
+      </c>
     </row>
     <row r="40" spans="1:8" ht="15.75">
-      <c r="A40" s="12"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="9"/>
+      <c r="A40" s="7">
+        <v>38</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D40" s="15">
+        <v>8460068533</v>
+      </c>
     </row>
     <row r="41" spans="1:8" ht="15.75">
-      <c r="A41" s="12"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="9"/>
+      <c r="A41" s="7">
+        <v>39</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D41" s="15">
+        <v>9586961070</v>
+      </c>
     </row>
     <row r="42" spans="1:8" ht="15.75">
-      <c r="A42" s="12"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="9"/>
+      <c r="A42" s="7">
+        <v>40</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D42" s="15">
+        <v>9510187989</v>
+      </c>
     </row>
     <row r="43" spans="1:8" ht="15.75">
-      <c r="A43" s="12"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="9"/>
+      <c r="A43" s="7">
+        <v>41</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D43" s="15">
+        <v>9825731288</v>
+      </c>
     </row>
     <row r="44" spans="1:8" ht="15.75">
-      <c r="A44" s="12"/>
-      <c r="B44" s="8"/>
-      <c r="C44" s="9"/>
+      <c r="A44" s="2">
+        <v>42</v>
+      </c>
+      <c r="B44" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C44" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D44" s="15">
+        <v>9909916131</v>
+      </c>
     </row>
     <row r="45" spans="1:8" ht="15.75">
-      <c r="A45" s="12"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="9"/>
-    </row>
-    <row r="46" spans="1:8" ht="15.75">
-      <c r="A46" s="12"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="9"/>
-    </row>
-    <row r="47" spans="1:8" ht="15.75">
-      <c r="A47" s="12"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="9"/>
-    </row>
-    <row r="48" spans="1:8" ht="15.75">
-      <c r="A48" s="12"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="9"/>
-    </row>
-    <row r="49" spans="1:3" ht="15.75">
-      <c r="A49" s="12"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="9"/>
-    </row>
-    <row r="50" spans="1:3" ht="15.75">
-      <c r="A50" s="12"/>
-      <c r="B50" s="8"/>
-      <c r="C50" s="9"/>
-    </row>
-    <row r="51" spans="1:3" ht="15.75">
-      <c r="A51" s="12"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="9"/>
-    </row>
-    <row r="52" spans="1:3" ht="15.75">
-      <c r="A52" s="12"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="9"/>
-    </row>
-    <row r="53" spans="1:3" ht="15.75">
-      <c r="A53" s="12"/>
-      <c r="B53" s="8"/>
-      <c r="C53" s="9"/>
-    </row>
-    <row r="54" spans="1:3" ht="15.75">
-      <c r="A54" s="12"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="9"/>
+      <c r="A45" s="2">
+        <v>43</v>
+      </c>
+      <c r="B45" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C45" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="D45" s="2">
+        <v>9904155896</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
